--- a/premise/data/additional_inventories/lci-nuclear_SMR.xlsx
+++ b/premise/data/additional_inventories/lci-nuclear_SMR.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10308"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/romain/GitHub/premise/premise/data/additional_inventories/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{401ECCB8-CAFD-3E42-B21A-1C46F0EEDC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D4DDBE5-F15E-E049-A1FD-A96E35B32CE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38520" yWindow="-1060" windowWidth="25820" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="nuclear electricity" sheetId="1" r:id="rId1"/>
@@ -275,9 +275,6 @@
     <t>market for low level radioactive waste</t>
   </si>
   <si>
-    <t>electricity production, Small Modular Reactor (SMR)</t>
-  </si>
-  <si>
     <t>water</t>
   </si>
   <si>
@@ -454,6 +451,9 @@
 The infrastructure dataset input (nuclear power plant) has been re-calculated on the basis of the load factor of 90% and a lifetime of 60 years: 1/(160 MW * 60 years * 365 d/y * 24 h/d * 90%)*(160 MWe/1000 MWe)
 The yield of low radioactive waste and spent nuclear fuel has been increased by a factor of 2.18 , and 1.72, respectively.
 This is a very rough approximation. This dataset should NOT be used if its contribution is important to the system.</t>
+  </si>
+  <si>
+    <t>electricity production, nuclear, Small Modular Reactor (SMR)</t>
   </si>
 </sst>
 </file>
@@ -497,11 +497,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -820,7 +819,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
@@ -828,15 +827,15 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>137</v>
+      <c r="B4" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
@@ -912,7 +911,7 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -1092,7 +1091,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B21" s="2">
         <v>3.3456000000000006E-6</v>
@@ -1107,7 +1106,7 @@
         <v>27</v>
       </c>
       <c r="H21" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -1152,7 +1151,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B24" s="2">
         <v>2.176E-6</v>
@@ -1167,7 +1166,7 @@
         <v>27</v>
       </c>
       <c r="H24" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1212,7 +1211,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B27" s="2">
         <v>1.2240000000000001E-6</v>
@@ -1227,12 +1226,12 @@
         <v>27</v>
       </c>
       <c r="H27" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B28" s="2">
         <v>1.0485600000000002E-6</v>
@@ -1247,7 +1246,7 @@
         <v>27</v>
       </c>
       <c r="H28" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1332,7 +1331,7 @@
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B33" s="2">
         <v>8.7448000000000003E-8</v>
@@ -1432,7 +1431,7 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B38" s="2">
         <v>2.1139861322509725E-12</v>
@@ -1447,7 +1446,7 @@
         <v>27</v>
       </c>
       <c r="H38" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="O38" s="2"/>
       <c r="Q38" s="2"/>
@@ -1475,7 +1474,7 @@
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B40" s="2">
         <f>-0.0000000284*(1.2/0.55)</f>
@@ -1496,7 +1495,7 @@
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B41" s="2">
         <v>-1.3192000000000002E-6</v>
@@ -1516,7 +1515,7 @@
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B42" s="2">
         <v>-2.2168000000000001E-6</v>
@@ -1531,12 +1530,12 @@
         <v>27</v>
       </c>
       <c r="H42" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B43" s="2">
         <v>-2.9784000000000006E-6</v>
@@ -1551,12 +1550,12 @@
         <v>27</v>
       </c>
       <c r="H43" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="2">
         <f>-0.000002464*(11/6.4)</f>
@@ -1594,7 +1593,7 @@
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2">
         <v>4.3112000000000001E-10</v>
@@ -1611,7 +1610,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2">
         <v>4.2568000000000004E-9</v>
@@ -1628,7 +1627,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B48" s="2">
         <v>2.2304000000000002E-8</v>
@@ -1645,7 +1644,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B49" s="2">
         <v>6.5552000000000004E-7</v>
@@ -1662,7 +1661,7 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B50" s="2">
         <v>1.2294400000000001E-6</v>
@@ -1679,7 +1678,7 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B51" s="2">
         <v>5.6576000000000011E-7</v>
@@ -1696,7 +1695,7 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2">
         <v>2.4752E-6</v>
@@ -1713,7 +1712,7 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B53" s="2">
         <v>6.4600000000000004E-10</v>
@@ -1730,7 +1729,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B54" s="2">
         <v>2.1352000000000003E-6</v>
@@ -1764,7 +1763,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B56" s="2">
         <v>2.0400000000000004E-6</v>
@@ -1781,7 +1780,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B57" s="2">
         <v>1.5232000000000002E-10</v>
@@ -1798,7 +1797,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B58" s="2">
         <v>3.5768000000000006E-7</v>
@@ -1849,7 +1848,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B61" s="2">
         <v>1.1451200000000001E-7</v>
@@ -1866,7 +1865,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B62" s="2">
         <v>9.9007999999999996E-9</v>
@@ -1883,7 +1882,7 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B63" s="2">
         <v>3.8216000000000008E-6</v>
@@ -1900,7 +1899,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B64" s="2">
         <v>1.02816E-5</v>
@@ -1934,7 +1933,7 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B66" s="2">
         <v>1.0295200000000001E-7</v>
@@ -1951,7 +1950,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B67" s="2">
         <v>4.1752000000000003E-6</v>
@@ -1968,7 +1967,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B68">
         <v>0.10021784572074248</v>
@@ -1977,7 +1976,7 @@
         <v>24</v>
       </c>
       <c r="E68" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F68" t="s">
         <v>18</v>
@@ -1985,7 +1984,7 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B69">
         <v>3.9668981352986863E-3</v>
@@ -1994,7 +1993,7 @@
         <v>24</v>
       </c>
       <c r="E69" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F69" t="s">
         <v>18</v>
@@ -2002,7 +2001,7 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B70">
         <v>0.10032584000000001</v>
@@ -2019,7 +2018,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B71">
         <v>1.5504E-3</v>
@@ -2036,7 +2035,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B72" s="2">
         <v>6.7320000000000007E-7</v>
@@ -2070,7 +2069,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B74" s="2">
         <v>1.7680000000000003E-6</v>
@@ -2087,7 +2086,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B75">
         <v>0.82144000000000006</v>
@@ -2104,7 +2103,7 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B76" s="2">
         <v>5.6712000000000002E-5</v>
@@ -2121,7 +2120,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B77" s="2">
         <v>1.1791200000000002E-7</v>
@@ -2138,7 +2137,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B78" s="2">
         <v>4.9640000000000002E-6</v>
@@ -2155,7 +2154,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B79" s="2">
         <v>6.0248000000000003E-6</v>
@@ -2172,7 +2171,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B80">
         <v>0.22576000000000002</v>
@@ -2189,7 +2188,7 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B81">
         <v>1.3600000000000003E-4</v>
@@ -2206,7 +2205,7 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B82" s="2">
         <v>8.1599999999999999E-9</v>
@@ -2223,7 +2222,7 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B83" s="2">
         <v>1.35728E-5</v>
@@ -2240,7 +2239,7 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B84" s="2">
         <v>5.1272000000000006E-6</v>
@@ -2257,7 +2256,7 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B85" s="2">
         <v>5.6168000000000008E-5</v>
@@ -2274,7 +2273,7 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B86" s="2">
         <v>5.7120000000000003E-7</v>
@@ -2291,7 +2290,7 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B87" s="2">
         <v>1.21312E-5</v>
@@ -2308,7 +2307,7 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B88" s="2">
         <v>7.8608000000000011E-8</v>
@@ -2325,7 +2324,7 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B89" s="2">
         <v>3.8760000000000006E-7</v>
@@ -2342,7 +2341,7 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B90" s="2">
         <v>3.8216000000000003E-7</v>
@@ -2359,7 +2358,7 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B91">
         <v>1.3423200000000001E-2</v>
@@ -2376,7 +2375,7 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B92" s="2">
         <v>2.3935999999999999E-7</v>
@@ -2393,7 +2392,7 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B93">
         <v>1.0390400000000001E-2</v>
@@ -2410,7 +2409,7 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B94">
         <v>5.3720000000000005E-4</v>
@@ -2427,7 +2426,7 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B95" s="2">
         <v>3.1824000000000001E-8</v>
@@ -2444,7 +2443,7 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B96" s="2">
         <v>1.7816E-5</v>
